--- a/output/Tables/Scenarios/HIA_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_scenarios.xlsx
@@ -1,21 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Scenarios/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118D7C16-E632-CF41-9F12-2451D527F058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>2019 baseline</t>
+  </si>
+  <si>
+    <t>Best case scenario</t>
+  </si>
+  <si>
+    <t>Modal shift scenario</t>
+  </si>
+  <si>
+    <t>Best practice scenario</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +134,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +186,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +220,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,140 +431,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>15</v>
       </c>
       <c r="B2">
-        <v>276215.276</v>
+        <v>276215.27600000001</v>
       </c>
       <c r="C2">
-        <v>264254.083</v>
+        <v>264254.08299999998</v>
       </c>
       <c r="D2">
         <v>288334.913</v>
       </c>
       <c r="E2">
-        <v>764692.493</v>
+        <v>764692.49300000002</v>
       </c>
       <c r="F2">
-        <v>738967.635</v>
+        <v>738967.63500000001</v>
       </c>
       <c r="G2">
-        <v>790752.768</v>
+        <v>790752.76800000004</v>
       </c>
       <c r="H2">
-        <v>3414882302.139999</v>
+        <v>3414882302.1399989</v>
       </c>
       <c r="I2">
-        <v>3258736761.879</v>
+        <v>3258736761.8790002</v>
       </c>
       <c r="J2">
-        <v>3573276711.887</v>
+        <v>3573276711.8870001</v>
       </c>
       <c r="K2">
         <v>101706015831.241</v>
       </c>
       <c r="L2">
-        <v>98265373980.851</v>
+        <v>98265373980.850998</v>
       </c>
       <c r="M2">
         <v>105168690068.69</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2019 baseline</t>
-        </is>
+      <c r="N2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
       </c>
       <c r="B3">
         <v>1025387.215</v>
@@ -501,131 +556,119 @@
         <v>2236378.145</v>
       </c>
       <c r="G3">
-        <v>2319970.947</v>
+        <v>2319970.9470000002</v>
       </c>
       <c r="H3">
-        <v>13000395825.457</v>
+        <v>13000395825.457001</v>
       </c>
       <c r="I3">
-        <v>12689883487.339</v>
+        <v>12689883487.339001</v>
       </c>
       <c r="J3">
         <v>13314821064.444</v>
       </c>
       <c r="K3">
-        <v>302974325767.796</v>
+        <v>302974325767.79602</v>
       </c>
       <c r="L3">
-        <v>297413048988.73</v>
+        <v>297413048988.72998</v>
       </c>
       <c r="M3">
-        <v>308547875002.449</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Best case scenario</t>
-        </is>
+        <v>308547875002.44897</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>345005.58</v>
       </c>
       <c r="C4">
-        <v>330884.732</v>
+        <v>330884.73200000002</v>
       </c>
       <c r="D4">
-        <v>359385.669</v>
+        <v>359385.66899999999</v>
       </c>
       <c r="E4">
-        <v>922703.7050000001</v>
+        <v>922703.70500000007</v>
       </c>
       <c r="F4">
         <v>893364.848</v>
       </c>
       <c r="G4">
-        <v>952550.3429999999</v>
+        <v>952550.34299999988</v>
       </c>
       <c r="H4">
-        <v>4279917804.558</v>
+        <v>4279917804.5580001</v>
       </c>
       <c r="I4">
-        <v>4095447030.794</v>
+        <v>4095447030.7940001</v>
       </c>
       <c r="J4">
-        <v>4468322005.476</v>
+        <v>4468322005.4759998</v>
       </c>
       <c r="K4">
-        <v>122720349655.447</v>
+        <v>122720349655.44701</v>
       </c>
       <c r="L4">
-        <v>118808174355.626</v>
+        <v>118808174355.62601</v>
       </c>
       <c r="M4">
         <v>126691546976.211</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Modal shift scenario</t>
-        </is>
+      <c r="N4" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>335304.807</v>
+        <v>335304.80699999997</v>
       </c>
       <c r="C5">
-        <v>318393.171</v>
+        <v>318393.17099999997</v>
       </c>
       <c r="D5">
-        <v>352318.105</v>
+        <v>352318.10499999998</v>
       </c>
       <c r="E5">
-        <v>1143344.455</v>
+        <v>1143344.4550000001</v>
       </c>
       <c r="F5">
-        <v>1097929.945</v>
+        <v>1097929.9450000001</v>
       </c>
       <c r="G5">
-        <v>1188943.542</v>
+        <v>1188943.5419999999</v>
       </c>
       <c r="H5">
-        <v>4294053153.555</v>
+        <v>4294053153.5549998</v>
       </c>
       <c r="I5">
-        <v>4070190513.913</v>
+        <v>4070190513.9130001</v>
       </c>
       <c r="J5">
-        <v>4520578907.734</v>
+        <v>4520578907.7340002</v>
       </c>
       <c r="K5">
         <v>152071087801.185</v>
       </c>
       <c r="L5">
-        <v>146012688697.083</v>
+        <v>146012688697.08301</v>
       </c>
       <c r="M5">
         <v>158163783558.4971</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Best practice scenario</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="N5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Scenarios/HIA_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_scenarios.xlsx
@@ -1,92 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Scenarios/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118D7C16-E632-CF41-9F12-2451D527F058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>area_type</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>2019 baseline</t>
-  </si>
-  <si>
-    <t>Best case scenario</t>
-  </si>
-  <si>
-    <t>Modal shift scenario</t>
-  </si>
-  <si>
-    <t>Best practice scenario</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -186,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -220,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -431,114 +350,140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>area_type</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>15</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B2">
-        <v>276215.27600000001</v>
+        <v>276215.276</v>
       </c>
       <c r="C2">
-        <v>264254.08299999998</v>
+        <v>264254.083</v>
       </c>
       <c r="D2">
         <v>288334.913</v>
       </c>
       <c r="E2">
-        <v>764692.49300000002</v>
+        <v>764692.493</v>
       </c>
       <c r="F2">
-        <v>738967.63500000001</v>
+        <v>738967.635</v>
       </c>
       <c r="G2">
-        <v>790752.76800000004</v>
+        <v>790752.768</v>
       </c>
       <c r="H2">
-        <v>3414882302.1399989</v>
+        <v>3414882302.14</v>
       </c>
       <c r="I2">
-        <v>3258736761.8790002</v>
+        <v>3258736761.879</v>
       </c>
       <c r="J2">
-        <v>3573276711.8870001</v>
+        <v>3573276711.887</v>
       </c>
       <c r="K2">
         <v>101706015831.241</v>
       </c>
       <c r="L2">
-        <v>98265373980.850998</v>
+        <v>98265373980.851</v>
       </c>
       <c r="M2">
         <v>105168690068.69</v>
       </c>
-      <c r="N2" t="s">
-        <v>16</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2019 baseline</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B3">
         <v>1025387.215</v>
@@ -556,119 +501,131 @@
         <v>2236378.145</v>
       </c>
       <c r="G3">
-        <v>2319970.9470000002</v>
+        <v>2319970.947</v>
       </c>
       <c r="H3">
-        <v>13000395825.457001</v>
+        <v>13000395825.457</v>
       </c>
       <c r="I3">
-        <v>12689883487.339001</v>
+        <v>12689883487.339</v>
       </c>
       <c r="J3">
         <v>13314821064.444</v>
       </c>
       <c r="K3">
-        <v>302974325767.79602</v>
+        <v>302974325767.796</v>
       </c>
       <c r="L3">
-        <v>297413048988.72998</v>
+        <v>297413048988.73</v>
       </c>
       <c r="M3">
-        <v>308547875002.44897</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
+        <v>308547875002.449</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Best case scenario</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B4">
         <v>345005.58</v>
       </c>
       <c r="C4">
-        <v>330884.73200000002</v>
+        <v>330884.732</v>
       </c>
       <c r="D4">
-        <v>359385.66899999999</v>
+        <v>359385.669</v>
       </c>
       <c r="E4">
-        <v>922703.70500000007</v>
+        <v>922703.7050000001</v>
       </c>
       <c r="F4">
         <v>893364.848</v>
       </c>
       <c r="G4">
-        <v>952550.34299999988</v>
+        <v>952550.3429999999</v>
       </c>
       <c r="H4">
-        <v>4279917804.5580001</v>
+        <v>4279917804.558</v>
       </c>
       <c r="I4">
-        <v>4095447030.7940001</v>
+        <v>4095447030.794</v>
       </c>
       <c r="J4">
-        <v>4468322005.4759998</v>
+        <v>4468322005.476</v>
       </c>
       <c r="K4">
-        <v>122720349655.44701</v>
+        <v>122720349655.447</v>
       </c>
       <c r="L4">
-        <v>118808174355.62601</v>
+        <v>118808174355.626</v>
       </c>
       <c r="M4">
         <v>126691546976.211</v>
       </c>
-      <c r="N4" t="s">
-        <v>18</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Modal shift scenario</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B5">
-        <v>335304.80699999997</v>
+        <v>469230.3959999999</v>
       </c>
       <c r="C5">
-        <v>318393.17099999997</v>
+        <v>443594.0599999999</v>
       </c>
       <c r="D5">
-        <v>352318.10499999998</v>
+        <v>495019.531</v>
       </c>
       <c r="E5">
-        <v>1143344.4550000001</v>
+        <v>1360769.854</v>
       </c>
       <c r="F5">
-        <v>1097929.9450000001</v>
+        <v>1302804.038</v>
       </c>
       <c r="G5">
-        <v>1188943.5419999999</v>
+        <v>1419177.977</v>
       </c>
       <c r="H5">
-        <v>4294053153.5549998</v>
+        <v>5719630979.415</v>
       </c>
       <c r="I5">
-        <v>4070190513.9130001</v>
+        <v>5401166550.584999</v>
       </c>
       <c r="J5">
-        <v>4520578907.7340002</v>
+        <v>6042086448.152999</v>
       </c>
       <c r="K5">
-        <v>152071087801.185</v>
+        <v>180989084746.239</v>
       </c>
       <c r="L5">
-        <v>146012688697.08301</v>
+        <v>173269368266.2661</v>
       </c>
       <c r="M5">
-        <v>158163783558.4971</v>
-      </c>
-      <c r="N5" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" t="s">
-        <v>15</v>
+        <v>188790744292.316</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Best practice scenario</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
   </sheetData>
